--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Technology Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Technology Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="219">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Technology Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -88,6 +88,12 @@
     <t>Telecom - Services</t>
   </si>
   <si>
+    <t>Bharti Airtel Ltd. - Partly Paid Share</t>
+  </si>
+  <si>
+    <t>IN9397D01014</t>
+  </si>
+  <si>
     <t>LTIMindtree Ltd.</t>
   </si>
   <si>
@@ -106,10 +112,13 @@
     <t>INE860A01027</t>
   </si>
   <si>
-    <t>Bharti Airtel Ltd. - Partly Paid Share</t>
-  </si>
-  <si>
-    <t>IN9397D01014</t>
+    <t>Zomato Ltd.</t>
+  </si>
+  <si>
+    <t>INE758T01015</t>
+  </si>
+  <si>
+    <t>Retailing</t>
   </si>
   <si>
     <t>Wipro Ltd.</t>
@@ -118,31 +127,64 @@
     <t>INE075A01022</t>
   </si>
   <si>
-    <t>Zomato Ltd.</t>
-  </si>
-  <si>
-    <t>INE758T01015</t>
-  </si>
-  <si>
-    <t>Retailing</t>
-  </si>
-  <si>
     <t>Persistent Systems Ltd.</t>
   </si>
   <si>
     <t>INE262H01021</t>
   </si>
   <si>
+    <t>Info Edge (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE663F01032</t>
+  </si>
+  <si>
     <t>Mphasis Ltd.</t>
   </si>
   <si>
     <t>INE356A01018</t>
   </si>
   <si>
-    <t>Info Edge (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE663F01024</t>
+    <t>COFORGE Ltd.</t>
+  </si>
+  <si>
+    <t>INE591G01017</t>
+  </si>
+  <si>
+    <t>Cyient Ltd.</t>
+  </si>
+  <si>
+    <t>INE136B01020</t>
+  </si>
+  <si>
+    <t>It - Services</t>
+  </si>
+  <si>
+    <t>Sagility India Ltd</t>
+  </si>
+  <si>
+    <t>INE0W2G01015</t>
+  </si>
+  <si>
+    <t>Multi Commodity Exchange Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE745G01035</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Indiamart Intermesh Ltd.</t>
+  </si>
+  <si>
+    <t>INE933S01016</t>
+  </si>
+  <si>
+    <t>Hexaware Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE093A01041</t>
   </si>
   <si>
     <t>Birlasoft Ltd.</t>
@@ -151,13 +193,25 @@
     <t>INE836A01035</t>
   </si>
   <si>
-    <t>Cyient Ltd.</t>
-  </si>
-  <si>
-    <t>INE136B01020</t>
-  </si>
-  <si>
-    <t>It - Services</t>
+    <t>Zensar Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE520A01027</t>
+  </si>
+  <si>
+    <t>Zee Entertainment Enterprises Ltd.</t>
+  </si>
+  <si>
+    <t>INE256A01028</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>L&amp;T Technology Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE010V01017</t>
   </si>
   <si>
     <t>Rategain Travel Technologies Ltd.</t>
@@ -166,22 +220,100 @@
     <t>INE0CLI01024</t>
   </si>
   <si>
-    <t>Zensar Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE520A01027</t>
-  </si>
-  <si>
-    <t>Indiamart Intermesh Ltd.</t>
-  </si>
-  <si>
-    <t>INE933S01016</t>
-  </si>
-  <si>
-    <t>COFORGE Ltd.</t>
-  </si>
-  <si>
-    <t>INE591G01017</t>
+    <t>Eclerx Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE738I01010</t>
+  </si>
+  <si>
+    <t>Commercial Services &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Sonata Software Ltd.</t>
+  </si>
+  <si>
+    <t>INE269A01021</t>
+  </si>
+  <si>
+    <t>Cigniti Technologies Ltd</t>
+  </si>
+  <si>
+    <t>INE675C01017</t>
+  </si>
+  <si>
+    <t>Mastek Ltd.</t>
+  </si>
+  <si>
+    <t>INE759A01021</t>
+  </si>
+  <si>
+    <t>PB Fintech Ltd.</t>
+  </si>
+  <si>
+    <t>INE417T01026</t>
+  </si>
+  <si>
+    <t>Financial Technology (Fintech)</t>
+  </si>
+  <si>
+    <t>FSN E-Commerce Ventures Ltd.</t>
+  </si>
+  <si>
+    <t>INE388Y01029</t>
+  </si>
+  <si>
+    <t>Bharti Hexacom Ltd.</t>
+  </si>
+  <si>
+    <t>INE343G01021</t>
+  </si>
+  <si>
+    <t>Swiggy Ltd</t>
+  </si>
+  <si>
+    <t>INE00H001014</t>
+  </si>
+  <si>
+    <t>C.E.Info Systems Ltd.</t>
+  </si>
+  <si>
+    <t>INE0BV301023</t>
+  </si>
+  <si>
+    <t>TBO Tek Ltd.</t>
+  </si>
+  <si>
+    <t>INE673O01025</t>
+  </si>
+  <si>
+    <t>Leisure Services</t>
+  </si>
+  <si>
+    <t>Yatra Online Ltd</t>
+  </si>
+  <si>
+    <t>INE0JR601024</t>
+  </si>
+  <si>
+    <t>Tata Elxsi Ltd.</t>
+  </si>
+  <si>
+    <t>INE670A01012</t>
+  </si>
+  <si>
+    <t>Firstsource Solutions Ltd.</t>
+  </si>
+  <si>
+    <t>INE684F01012</t>
+  </si>
+  <si>
+    <t>CYIENT DLM LTD</t>
+  </si>
+  <si>
+    <t>INE055S01018</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
   </si>
   <si>
     <t>KPIT Technologies Ltd</t>
@@ -190,49 +322,16 @@
     <t>INE04I401011</t>
   </si>
   <si>
-    <t>L&amp;T Technology Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE010V01017</t>
-  </si>
-  <si>
-    <t>Sagility India Ltd</t>
-  </si>
-  <si>
-    <t>INE0W2G01015</t>
-  </si>
-  <si>
-    <t>Multi Commodity Exchange Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE745G01035</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Mastek Ltd.</t>
-  </si>
-  <si>
-    <t>INE759A01021</t>
-  </si>
-  <si>
-    <t>Cartrade Tech Ltd</t>
-  </si>
-  <si>
-    <t>INE290S01011</t>
-  </si>
-  <si>
-    <t>C.E.Info Systems Ltd.</t>
-  </si>
-  <si>
-    <t>INE0BV301023</t>
-  </si>
-  <si>
-    <t>Cigniti Technologies Ltd</t>
-  </si>
-  <si>
-    <t>INE675C01017</t>
+    <t>Sun TV Network Ltd.</t>
+  </si>
+  <si>
+    <t>INE424H01027</t>
+  </si>
+  <si>
+    <t>Affle India Ltd.</t>
+  </si>
+  <si>
+    <t>INE00WC01027</t>
   </si>
   <si>
     <t>Netweb Technologies India</t>
@@ -241,79 +340,91 @@
     <t>INE0NT901020</t>
   </si>
   <si>
+    <t>PVR INOX Ltd.</t>
+  </si>
+  <si>
+    <t>INE191H01014</t>
+  </si>
+  <si>
+    <t>Rashi Peripherals Ltd</t>
+  </si>
+  <si>
+    <t>INE0J1F01024</t>
+  </si>
+  <si>
+    <t>It - Hardware</t>
+  </si>
+  <si>
+    <t>Teamlease Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE985S01024</t>
+  </si>
+  <si>
+    <t>NIIT Learning Systems Ltd</t>
+  </si>
+  <si>
+    <t>INE342G01023</t>
+  </si>
+  <si>
+    <t>Other Consumer Services</t>
+  </si>
+  <si>
+    <t>Delhivery Ltd.</t>
+  </si>
+  <si>
+    <t>INE148O01028</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>Tata Technologies Ltd</t>
+  </si>
+  <si>
+    <t>INE142M01025</t>
+  </si>
+  <si>
+    <t>Route Mobile Ltd.</t>
+  </si>
+  <si>
+    <t>INE450U01017</t>
+  </si>
+  <si>
+    <t>Siemens Ltd.</t>
+  </si>
+  <si>
+    <t>INE003A01024</t>
+  </si>
+  <si>
+    <t>Electrical Equipment</t>
+  </si>
+  <si>
+    <t>Onward Technologies Ltd</t>
+  </si>
+  <si>
+    <t>INE229A01017</t>
+  </si>
+  <si>
     <t>Axiscades Technologies Ltd.</t>
   </si>
   <si>
     <t>INE555B01013</t>
   </si>
   <si>
-    <t>Hitachi Energy India Ltd.</t>
-  </si>
-  <si>
-    <t>INE07Y701011</t>
-  </si>
-  <si>
-    <t>Electrical Equipment</t>
-  </si>
-  <si>
-    <t>Eclerx Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE738I01010</t>
-  </si>
-  <si>
-    <t>Commercial Services &amp; Supplies</t>
-  </si>
-  <si>
-    <t>Firstsource Solutions Ltd.</t>
-  </si>
-  <si>
-    <t>INE684F01012</t>
-  </si>
-  <si>
-    <t>Tata Elxsi Ltd.</t>
-  </si>
-  <si>
-    <t>INE670A01012</t>
-  </si>
-  <si>
-    <t>Yatra Online Ltd</t>
-  </si>
-  <si>
-    <t>INE0JR601024</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>FSN E-Commerce Ventures Ltd.</t>
-  </si>
-  <si>
-    <t>INE388Y01029</t>
-  </si>
-  <si>
-    <t>CYIENT DLM LTD</t>
-  </si>
-  <si>
-    <t>INE055S01018</t>
-  </si>
-  <si>
-    <t>Industrial Manufacturing</t>
-  </si>
-  <si>
-    <t>Sonata Software Ltd.</t>
-  </si>
-  <si>
-    <t>INE269A01021</t>
-  </si>
-  <si>
-    <t>Sun TV Network Ltd.</t>
-  </si>
-  <si>
-    <t>INE424H01027</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
+    <t>SIEMENS ENERGY INDIA LTD</t>
+  </si>
+  <si>
+    <t>INE1NPP01017</t>
+  </si>
+  <si>
+    <t>Go Digit General Insurance Ltd</t>
+  </si>
+  <si>
+    <t>INE03JT01014</t>
+  </si>
+  <si>
+    <t>Insurance</t>
   </si>
   <si>
     <t>Intellect Design Arena Ltd.</t>
@@ -322,139 +433,22 @@
     <t>INE306R01017</t>
   </si>
   <si>
+    <t>Updater Services Ltd</t>
+  </si>
+  <si>
+    <t>INE851I01011</t>
+  </si>
+  <si>
     <t>Zaggle Prepaid Ocean Services Ltd.</t>
   </si>
   <si>
     <t>INE07K301024</t>
   </si>
   <si>
-    <t>Zee Entertainment Enterprises Ltd.</t>
-  </si>
-  <si>
-    <t>INE256A01028</t>
-  </si>
-  <si>
-    <t>Swiggy Ltd</t>
-  </si>
-  <si>
-    <t>INE00H001014</t>
-  </si>
-  <si>
-    <t>Affle India Ltd.</t>
-  </si>
-  <si>
-    <t>INE00WC01027</t>
-  </si>
-  <si>
-    <t>PVR INOX Ltd.</t>
-  </si>
-  <si>
-    <t>INE191H01014</t>
-  </si>
-  <si>
-    <t>Hindustan Aeronautics Ltd.</t>
-  </si>
-  <si>
-    <t>INE066F01020</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
-    <t>NIIT Learning Systems Ltd</t>
-  </si>
-  <si>
-    <t>INE342G01023</t>
-  </si>
-  <si>
-    <t>Other Consumer Services</t>
-  </si>
-  <si>
-    <t>Rashi Peripherals Ltd</t>
-  </si>
-  <si>
-    <t>INE0J1F01024</t>
-  </si>
-  <si>
-    <t>It - Hardware</t>
-  </si>
-  <si>
-    <t>Siemens Ltd.</t>
-  </si>
-  <si>
-    <t>INE003A01024</t>
-  </si>
-  <si>
-    <t>Ge Vernova T&amp;D India Ltd.</t>
-  </si>
-  <si>
-    <t>INE200A01026</t>
-  </si>
-  <si>
-    <t>Tata Technologies Ltd</t>
-  </si>
-  <si>
-    <t>INE142M01025</t>
-  </si>
-  <si>
-    <t>Bharti Hexacom Ltd.</t>
-  </si>
-  <si>
-    <t>INE343G01021</t>
-  </si>
-  <si>
-    <t>Delhivery Ltd.</t>
-  </si>
-  <si>
-    <t>INE148O01028</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>BSE Ltd.</t>
-  </si>
-  <si>
-    <t>INE118H01025</t>
-  </si>
-  <si>
-    <t>Teamlease Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE985S01024</t>
-  </si>
-  <si>
-    <t>Route Mobile Ltd.</t>
-  </si>
-  <si>
-    <t>INE450U01017</t>
-  </si>
-  <si>
-    <t>Onward Technologies Ltd</t>
-  </si>
-  <si>
-    <t>INE229A01017</t>
-  </si>
-  <si>
-    <t>Jyoti CNC Automation Ltd</t>
-  </si>
-  <si>
-    <t>INE980O01024</t>
-  </si>
-  <si>
-    <t>Updater Services Ltd</t>
-  </si>
-  <si>
-    <t>INE851I01011</t>
-  </si>
-  <si>
-    <t>Go Digit General Insurance Ltd</t>
-  </si>
-  <si>
-    <t>INE03JT01014</t>
-  </si>
-  <si>
-    <t>Insurance</t>
+    <t>Redington (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE891D01026</t>
   </si>
   <si>
     <t>INOX India Ltd</t>
@@ -466,12 +460,6 @@
     <t>Industrial Products</t>
   </si>
   <si>
-    <t>Redington (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE891D01026</t>
-  </si>
-  <si>
     <t>Tracxn Technologies Ltd</t>
   </si>
   <si>
@@ -484,30 +472,18 @@
     <t>INE0I7C01011</t>
   </si>
   <si>
-    <t>NIIT Ltd.</t>
-  </si>
-  <si>
-    <t>INE161A01038</t>
-  </si>
-  <si>
-    <t>Nucleus Software Exports Ltd.</t>
-  </si>
-  <si>
-    <t>INE096B01018</t>
+    <t>Indegene Ltd.</t>
+  </si>
+  <si>
+    <t>INE065X01017</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
   </si>
   <si>
     <t>^</t>
   </si>
   <si>
-    <t>Indegene Ltd.</t>
-  </si>
-  <si>
-    <t>INE065X01017</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
     <t>Nazara technologies Ltd</t>
   </si>
   <si>
@@ -532,6 +508,15 @@
     <t>IE00B4BNMY34</t>
   </si>
   <si>
+    <t>Microsoft Corp</t>
+  </si>
+  <si>
+    <t>US5949181045</t>
+  </si>
+  <si>
+    <t>Systems Software</t>
+  </si>
+  <si>
     <t>Amazon com</t>
   </si>
   <si>
@@ -541,13 +526,10 @@
     <t>Internet &amp; Direct Marketing Retail</t>
   </si>
   <si>
-    <t>Microsoft Corp</t>
-  </si>
-  <si>
-    <t>US5949181045</t>
-  </si>
-  <si>
-    <t>Systems Software</t>
+    <t>Epam Systems Inc</t>
+  </si>
+  <si>
+    <t>US29414B1044</t>
   </si>
   <si>
     <t>Adobe Inc</t>
@@ -559,12 +541,6 @@
     <t>Application Software</t>
   </si>
   <si>
-    <t>Epam Systems Inc</t>
-  </si>
-  <si>
-    <t>US29414B1044</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -598,22 +574,31 @@
     <t>Treasury Bills</t>
   </si>
   <si>
+    <t>182 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002024Y407</t>
+  </si>
+  <si>
+    <t>SOV</t>
+  </si>
+  <si>
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X409</t>
-  </si>
-  <si>
-    <t>SOV</t>
-  </si>
-  <si>
-    <t>IN002024X383</t>
+    <t>IN002024X516</t>
+  </si>
+  <si>
+    <t>IN002025X026</t>
   </si>
   <si>
     <t>364 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002023Z489</t>
+    <t>IN002024Z164</t>
+  </si>
+  <si>
+    <t>IN002025X034</t>
   </si>
   <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
@@ -643,16 +628,10 @@
     <t>Stock / Index Futures</t>
   </si>
   <si>
-    <t>Bharti Airtel Ltd. $$</t>
-  </si>
-  <si>
-    <t>Birlasoft Ltd. $$</t>
-  </si>
-  <si>
-    <t>Mphasis Ltd $$</t>
-  </si>
-  <si>
-    <t>FSN E-Commerce Ventures Ltd. $$</t>
+    <t>Eternal Ltd. $$</t>
+  </si>
+  <si>
+    <t>INFO edge india Ltd $$</t>
   </si>
   <si>
     <t>Note- 1 : Index/ Stock futures are provided towards end of the table.</t>
@@ -679,7 +658,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -691,7 +670,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - BSE Teck TRI</t>
+    <t>Benchmark name - S&amp;P BSE Information Technology  TRI</t>
   </si>
 </sst>
 </file>
@@ -1088,13 +1067,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>157</xdr:row>
+      <xdr:row>153</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>167</xdr:row>
+      <xdr:row>163</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1112,7 +1091,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="30365700"/>
+          <a:off x="666750" y="29603700"/>
           <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1127,13 +1106,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>172</xdr:row>
+      <xdr:row>168</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>182</xdr:row>
+      <xdr:row>178</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1151,7 +1130,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="33223200"/>
+          <a:off x="666750" y="32461200"/>
           <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1485,7 +1464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J171"/>
+  <dimension ref="B1:J167"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
@@ -1493,7 +1472,7 @@
     <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="17.0" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="35.0" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="11.0" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="11.142857142857142" collapsed="true"/>
     <col min="7" max="7" bestFit="true" customWidth="true" style="22" width="38.714285714285715" collapsed="true"/>
     <col min="8" max="8" bestFit="true" customWidth="true" style="22" width="11.714285714285714" collapsed="true"/>
     <col min="9" max="9" bestFit="true" customWidth="true" style="22" width="29.714285714285715" collapsed="true"/>
@@ -1585,10 +1564,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>1343231.0099999998</v>
+        <v>1355992.8299999991</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9525468359749002</v>
+        <v>0.9755363130360998</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1622,10 +1601,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>1343231.0099999998</v>
+        <v>1355992.8299999991</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9525468359749002</v>
+        <v>0.9755363130360998</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1659,10 +1638,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>1298126.5499999998</v>
+        <v>1301359.1299999992</v>
       </c>
       <c r="H9" s="10">
-        <v>0.9205611906606002</v>
+        <v>0.9362314162209998</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1685,13 +1664,13 @@
         <v>18</v>
       </c>
       <c r="F10" s="14">
-        <v>15677009</v>
+        <v>16765417</v>
       </c>
       <c r="G10" s="15">
-        <v>294696.42</v>
+        <v>261993.17</v>
       </c>
       <c r="H10" s="16">
-        <v>0.2089827738902</v>
+        <v>0.1884846626389</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1714,13 +1693,13 @@
         <v>18</v>
       </c>
       <c r="F11" s="14">
-        <v>4315974</v>
+        <v>5220719</v>
       </c>
       <c r="G11" s="15">
-        <v>177490.11</v>
+        <v>180814.38</v>
       </c>
       <c r="H11" s="16">
-        <v>0.1258663933748</v>
+        <v>0.1300825415203</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1743,13 +1722,13 @@
         <v>23</v>
       </c>
       <c r="F12" s="14">
-        <v>5998853</v>
+        <v>6107014</v>
       </c>
       <c r="G12" s="15">
-        <v>97559.35</v>
+        <v>113358.39</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0691838183237</v>
+        <v>0.0815529576455</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1769,16 +1748,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F13" s="14">
-        <v>1555554</v>
+        <v>6179439</v>
       </c>
       <c r="G13" s="15">
-        <v>91997.80</v>
+        <v>86623.38</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0652398676434</v>
+        <v>0.0623190999824</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1801,13 +1780,13 @@
         <v>18</v>
       </c>
       <c r="F14" s="14">
-        <v>4302727</v>
+        <v>1481071</v>
       </c>
       <c r="G14" s="15">
-        <v>72047.01</v>
+        <v>75074.01</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0510918456366</v>
+        <v>0.0540101844937</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1830,13 +1809,13 @@
         <v>18</v>
       </c>
       <c r="F15" s="14">
-        <v>3758139</v>
+        <v>3902489</v>
       </c>
       <c r="G15" s="15">
-        <v>64844.81</v>
+        <v>61421.27</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0459844346469</v>
+        <v>0.0441880502259</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1856,16 +1835,16 @@
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F16" s="14">
-        <v>5291889</v>
+        <v>3564056</v>
       </c>
       <c r="G16" s="15">
-        <v>63462.98</v>
+        <v>58329.34</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0450045154934</v>
+        <v>0.0419636358148</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1885,16 +1864,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F17" s="14">
-        <v>15130114</v>
+        <v>18903419</v>
       </c>
       <c r="G17" s="15">
-        <v>47190.83</v>
+        <v>45048.74</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0334651861586</v>
+        <v>0.0324092286879</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1905,25 +1884,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F18" s="14">
-        <v>14449972</v>
+        <v>14803503</v>
       </c>
       <c r="G18" s="15">
-        <v>31840.51</v>
+        <v>36959.91</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0225795688386</v>
+        <v>0.026589915178</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1946,13 +1925,13 @@
         <v>18</v>
       </c>
       <c r="F19" s="14">
-        <v>510900</v>
+        <v>443401</v>
       </c>
       <c r="G19" s="15">
-        <v>30820.55</v>
+        <v>24998.95</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0218562683314</v>
+        <v>0.017984891198</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1972,16 +1951,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F20" s="14">
-        <v>1012193</v>
+        <v>1746760</v>
       </c>
       <c r="G20" s="15">
-        <v>29029.19</v>
+        <v>24935</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0205859326353</v>
+        <v>0.017938883914</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -2001,16 +1980,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F21" s="14">
-        <v>302934</v>
+        <v>921093</v>
       </c>
       <c r="G21" s="15">
-        <v>23397.71</v>
+        <v>23568.93</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0165923913784</v>
+        <v>0.0169560978242</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -2033,13 +2012,13 @@
         <v>18</v>
       </c>
       <c r="F22" s="14">
-        <v>3032156</v>
+        <v>244923</v>
       </c>
       <c r="G22" s="15">
-        <v>16209.91</v>
+        <v>20942.14</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0114951920905</v>
+        <v>0.0150663171594</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2062,13 +2041,13 @@
         <v>47</v>
       </c>
       <c r="F23" s="14">
-        <v>1088565</v>
+        <v>1430937</v>
       </c>
       <c r="G23" s="15">
-        <v>15832.63</v>
+        <v>19271.86</v>
       </c>
       <c r="H23" s="16">
-        <v>0.011227645505</v>
+        <v>0.0138646745276</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2088,16 +2067,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F24" s="14">
-        <v>2082626</v>
+        <v>46533598</v>
       </c>
       <c r="G24" s="15">
-        <v>14560.68</v>
+        <v>18394.73</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0103256473089</v>
+        <v>0.0132336445197</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2117,16 +2096,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="F25" s="14">
-        <v>1612296</v>
+        <v>260680</v>
       </c>
       <c r="G25" s="15">
-        <v>14026.98</v>
+        <v>17210.09</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0099471761133</v>
+        <v>0.0123813838644</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2137,25 +2116,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F26" s="14">
-        <v>580243</v>
+        <v>690343</v>
       </c>
       <c r="G26" s="15">
-        <v>11990.14</v>
+        <v>16102.25</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0085027592684</v>
+        <v>0.0115843751154</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2166,10 +2145,10 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>13</v>
@@ -2178,13 +2157,13 @@
         <v>18</v>
       </c>
       <c r="F27" s="14">
-        <v>143554</v>
+        <v>1703861</v>
       </c>
       <c r="G27" s="15">
-        <v>11863.09</v>
+        <v>14610.61</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0084126622749</v>
+        <v>0.01051125072</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2195,10 +2174,10 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>13</v>
@@ -2207,13 +2186,13 @@
         <v>18</v>
       </c>
       <c r="F28" s="14">
-        <v>752625</v>
+        <v>3409620</v>
       </c>
       <c r="G28" s="15">
-        <v>10605.99</v>
+        <v>13655.53</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0075211948962</v>
+        <v>0.009824141466</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2224,25 +2203,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="F29" s="14">
-        <v>185176</v>
+        <v>1451910</v>
       </c>
       <c r="G29" s="15">
-        <v>10090.89</v>
+        <v>12095.14</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0071559138153</v>
+        <v>0.0087015565423</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2253,25 +2232,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F30" s="14">
-        <v>19533598</v>
+        <v>9008040</v>
       </c>
       <c r="G30" s="15">
-        <v>9690.62</v>
+        <v>11748.29</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0068720639643</v>
+        <v>0.0084520236815</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2282,25 +2261,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="F31" s="14">
-        <v>154000</v>
+        <v>261776</v>
       </c>
       <c r="G31" s="15">
-        <v>8828.74</v>
+        <v>11433.33</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0062608652495</v>
+        <v>0.0082254333114</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2311,10 +2290,10 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
@@ -2323,13 +2302,13 @@
         <v>18</v>
       </c>
       <c r="F32" s="14">
-        <v>317595</v>
+        <v>2254201</v>
       </c>
       <c r="G32" s="15">
-        <v>8236.19</v>
+        <v>10004.14</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0058406608145</v>
+        <v>0.0071972370611</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2340,25 +2319,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="F33" s="14">
-        <v>495196</v>
+        <v>257416</v>
       </c>
       <c r="G33" s="15">
-        <v>8177.67</v>
+        <v>9117.93</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0057991615933</v>
+        <v>0.0065596746663</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2369,10 +2348,10 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>13</v>
@@ -2381,13 +2360,13 @@
         <v>18</v>
       </c>
       <c r="F34" s="14">
-        <v>474200</v>
+        <v>2066277</v>
       </c>
       <c r="G34" s="15">
-        <v>8068.04</v>
+        <v>8452.11</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0057214179224</v>
+        <v>0.0060806665377</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2398,10 +2377,10 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
@@ -2413,10 +2392,10 @@
         <v>525840</v>
       </c>
       <c r="G35" s="15">
-        <v>7788.48</v>
+        <v>8357.18</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0055231690795</v>
+        <v>0.0060123714404</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2427,25 +2406,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="F36" s="14">
-        <v>403185</v>
+        <v>327368</v>
       </c>
       <c r="G36" s="15">
-        <v>7233.34</v>
+        <v>7620.47</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0051294937946</v>
+        <v>0.0054823632123</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2456,25 +2435,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="F37" s="14">
-        <v>1061966</v>
+        <v>419958</v>
       </c>
       <c r="G37" s="15">
-        <v>7198.01</v>
+        <v>7397.98</v>
       </c>
       <c r="H37" s="16">
-        <v>0.005104439668</v>
+        <v>0.0053222981519</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2485,25 +2464,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="F38" s="14">
-        <v>52719</v>
+        <v>3581853</v>
       </c>
       <c r="G38" s="15">
-        <v>6781.53</v>
+        <v>7280.47</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0048090945611</v>
+        <v>0.0052377584186</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2514,25 +2493,25 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="F39" s="14">
-        <v>220333</v>
+        <v>393792</v>
       </c>
       <c r="G39" s="15">
-        <v>6738.11</v>
+        <v>7209.15</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0047783034438</v>
+        <v>0.005186448966</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2543,25 +2522,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="F40" s="14">
-        <v>1901967</v>
+        <v>2135673</v>
       </c>
       <c r="G40" s="15">
-        <v>6374.44</v>
+        <v>7112.86</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0045204083347</v>
+        <v>0.0051171754496</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2572,10 +2551,10 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>13</v>
@@ -2584,13 +2563,13 @@
         <v>18</v>
       </c>
       <c r="F41" s="14">
-        <v>91332</v>
+        <v>352926</v>
       </c>
       <c r="G41" s="15">
-        <v>5786.80</v>
+        <v>6833.35</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0041036858063</v>
+        <v>0.0049160887264</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2601,25 +2580,25 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F42" s="14">
-        <v>5976191</v>
+        <v>487938</v>
       </c>
       <c r="G42" s="15">
-        <v>5673.20</v>
+        <v>6366.13</v>
       </c>
       <c r="H42" s="16">
-        <v>0.004023126826</v>
+        <v>0.0045799585743</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2630,25 +2609,25 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>36</v>
-      </c>
       <c r="F43" s="14">
-        <v>3259053</v>
+        <v>6099694</v>
       </c>
       <c r="G43" s="15">
-        <v>5504.54</v>
+        <v>6094.20</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0039035222694</v>
+        <v>0.0043843250992</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2659,25 +2638,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="F44" s="14">
-        <v>1085378</v>
+        <v>91332</v>
       </c>
       <c r="G44" s="15">
-        <v>5298.27</v>
+        <v>5881.32</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0037572467335</v>
+        <v>0.0042311737213</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2697,16 +2676,16 @@
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="F45" s="14">
-        <v>999710</v>
+        <v>1454287</v>
       </c>
       <c r="G45" s="15">
-        <v>5288.47</v>
+        <v>5401.95</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0037502971031</v>
+        <v>0.0038863025449</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2729,13 +2708,13 @@
         <v>99</v>
       </c>
       <c r="F46" s="14">
-        <v>804728</v>
+        <v>1085378</v>
       </c>
       <c r="G46" s="15">
-        <v>4980.06</v>
+        <v>5252.14</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0035315893994</v>
+        <v>0.0037785253563</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2758,13 +2737,13 @@
         <v>18</v>
       </c>
       <c r="F47" s="14">
-        <v>523859</v>
+        <v>383025</v>
       </c>
       <c r="G47" s="15">
-        <v>4248.50</v>
+        <v>5124.11</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0030128065854</v>
+        <v>0.0036864172629</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2784,16 +2763,16 @@
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F48" s="14">
-        <v>898703</v>
+        <v>804728</v>
       </c>
       <c r="G48" s="15">
-        <v>3972.27</v>
+        <v>5066.97</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0028169191985</v>
+        <v>0.0036453092691</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2813,16 +2792,16 @@
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="F49" s="14">
-        <v>3717836</v>
+        <v>274362</v>
       </c>
       <c r="G49" s="15">
-        <v>3925.66</v>
+        <v>4761.83</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0027838659056</v>
+        <v>0.003425783661</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2842,16 +2821,16 @@
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F50" s="14">
-        <v>844684</v>
+        <v>218725</v>
       </c>
       <c r="G50" s="15">
-        <v>3514.73</v>
+        <v>4372.53</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0024924565587</v>
+        <v>0.0031457111722</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2871,16 +2850,16 @@
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F51" s="14">
-        <v>214486</v>
+        <v>293189</v>
       </c>
       <c r="G51" s="15">
-        <v>3234.34</v>
+        <v>2888.64</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0022936191247</v>
+        <v>0.0020781623272</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -2900,16 +2879,16 @@
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="F52" s="14">
-        <v>293189</v>
+        <v>886107</v>
       </c>
       <c r="G52" s="15">
-        <v>3197.23</v>
+        <v>2730.10</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0022673027183</v>
+        <v>0.0019641045507</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -2920,25 +2899,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D53" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="F53" s="14">
-        <v>75000</v>
+        <v>126777</v>
       </c>
       <c r="G53" s="15">
-        <v>2952.60</v>
+        <v>2479.38</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0020938243436</v>
+        <v>0.0017837300982</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -2964,10 +2943,10 @@
         <v>621706</v>
       </c>
       <c r="G54" s="15">
-        <v>2930.72</v>
+        <v>2046.35</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0020783082301</v>
+        <v>0.0014721971164</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -2990,13 +2969,13 @@
         <v>120</v>
       </c>
       <c r="F55" s="14">
-        <v>825854</v>
+        <v>500000</v>
       </c>
       <c r="G55" s="15">
-        <v>2854.15</v>
+        <v>1790</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0020240089245</v>
+        <v>0.0012877722962</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -3016,16 +2995,16 @@
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="F56" s="14">
-        <v>43275</v>
+        <v>224549</v>
       </c>
       <c r="G56" s="15">
-        <v>2628.24</v>
+        <v>1737.11</v>
       </c>
       <c r="H56" s="16">
-        <v>0.001863805762</v>
+        <v>0.0012497218622</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -3045,16 +3024,16 @@
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="F57" s="14">
-        <v>141633</v>
+        <v>149353</v>
       </c>
       <c r="G57" s="15">
-        <v>2531.69</v>
+        <v>1417.73</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0017953377201</v>
+        <v>0.0010199516298</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -3074,16 +3053,16 @@
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="F58" s="14">
-        <v>224549</v>
+        <v>43275</v>
       </c>
       <c r="G58" s="15">
-        <v>1768.55</v>
+        <v>1413.19</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0012541600768</v>
+        <v>0.0010166854364</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3094,25 +3073,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="F59" s="14">
-        <v>125709</v>
+        <v>442990</v>
       </c>
       <c r="G59" s="15">
-        <v>1703.23</v>
+        <v>1312.58</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0012078386631</v>
+        <v>0.0009443040003</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3123,25 +3102,25 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="F60" s="14">
-        <v>500000</v>
+        <v>118644</v>
       </c>
       <c r="G60" s="15">
-        <v>1605.25</v>
+        <v>1235.97</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0011383565425</v>
+        <v>0.0008891887848</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3161,16 +3140,16 @@
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="F61" s="14">
-        <v>29720</v>
+        <v>43275</v>
       </c>
       <c r="G61" s="15">
-        <v>1576.93</v>
+        <v>1072.42</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0011182735291</v>
+        <v>0.0007715266848</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3190,16 +3169,16 @@
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="F62" s="14">
-        <v>56777</v>
+        <v>286239</v>
       </c>
       <c r="G62" s="15">
-        <v>1386.58</v>
+        <v>987.52</v>
       </c>
       <c r="H62" s="16">
-        <v>0.0009832875968</v>
+        <v>0.000710447429</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3210,25 +3189,25 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F63" s="14">
-        <v>107778</v>
+        <v>78158</v>
       </c>
       <c r="G63" s="15">
-        <v>1290.1</v>
+        <v>916.44</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0009148691952</v>
+        <v>0.0006593106386</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3239,25 +3218,25 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="F64" s="14">
-        <v>442990</v>
+        <v>278715</v>
       </c>
       <c r="G64" s="15">
-        <v>1143.58</v>
+        <v>910.14</v>
       </c>
       <c r="H64" s="16">
-        <v>0.00081096513</v>
+        <v>0.0006547782556</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3268,25 +3247,25 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="F65" s="14">
-        <v>101072</v>
+        <v>208327</v>
       </c>
       <c r="G65" s="15">
-        <v>1087.33</v>
+        <v>902.58</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0007710756701</v>
+        <v>0.0006493393961</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3297,25 +3276,25 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F66" s="14">
-        <v>278715</v>
+        <v>193181</v>
       </c>
       <c r="G66" s="15">
-        <v>948.05</v>
+        <v>499.70</v>
       </c>
       <c r="H66" s="16">
-        <v>0.0006723058216</v>
+        <v>0.0003594971041</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3326,25 +3305,25 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F67" s="14">
-        <v>286239</v>
+        <v>34033</v>
       </c>
       <c r="G67" s="15">
-        <v>852.13</v>
+        <v>406.34</v>
       </c>
       <c r="H67" s="16">
-        <v>0.0006042845417</v>
+        <v>0.0002923315054</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3355,25 +3334,25 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>149</v>
+        <v>70</v>
       </c>
       <c r="F68" s="14">
-        <v>71574</v>
+        <v>333562</v>
       </c>
       <c r="G68" s="15">
-        <v>655.98</v>
+        <v>191.63</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0004651855628</v>
+        <v>0.0001378635782</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3393,16 +3372,16 @@
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="F69" s="14">
-        <v>193181</v>
+        <v>25435</v>
       </c>
       <c r="G69" s="15">
-        <v>398.40</v>
+        <v>105.82</v>
       </c>
       <c r="H69" s="16">
-        <v>0.000282523748</v>
+        <v>0.0000761296449</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3422,16 +3401,16 @@
         <v>13</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="F70" s="14">
-        <v>333562</v>
+        <v>2744</v>
       </c>
       <c r="G70" s="15">
-        <v>236.70</v>
-      </c>
-      <c r="H70" s="16">
-        <v>0.0001678548473</v>
+        <v>16.48</v>
+      </c>
+      <c r="H70" s="17" t="s">
+        <v>155</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3442,25 +3421,25 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C71" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F71" s="14">
+        <v>212</v>
+      </c>
+      <c r="G71" s="15">
+        <v>2.75</v>
+      </c>
+      <c r="H71" s="17" t="s">
         <v>155</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F71" s="14">
-        <v>25435</v>
-      </c>
-      <c r="G71" s="15">
-        <v>111.44</v>
-      </c>
-      <c r="H71" s="16">
-        <v>0.0000790272251</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>13</v>
@@ -3471,27 +3450,6 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="F72" s="14">
-        <v>62690</v>
-      </c>
-      <c r="G72" s="15">
-        <v>93.75</v>
-      </c>
-      <c r="H72" s="16">
-        <v>0.0000664824331</v>
-      </c>
-      <c r="I72" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J72" s="11" t="s">
@@ -3499,28 +3457,28 @@
       </c>
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
-      <c r="B73" s="12" t="s">
+      <c r="B73" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C73" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F73" s="14">
-        <v>6034</v>
-      </c>
-      <c r="G73" s="15">
-        <v>55.87</v>
-      </c>
-      <c r="H73" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="I73" s="15" t="s">
+      <c r="C73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="9">
+        <v>54633.70</v>
+      </c>
+      <c r="H73" s="10">
+        <v>0.0393048968151</v>
+      </c>
+      <c r="I73" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J73" s="11" t="s">
@@ -3529,25 +3487,25 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C74" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="13" t="s">
-        <v>163</v>
-      </c>
       <c r="F74" s="14">
-        <v>2744</v>
+        <v>374583</v>
       </c>
       <c r="G74" s="15">
-        <v>16.46</v>
-      </c>
-      <c r="H74" s="17" t="s">
-        <v>160</v>
+        <v>25931.81</v>
+      </c>
+      <c r="H74" s="16">
+        <v>0.0186560148093</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>13</v>
@@ -3558,25 +3516,25 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D75" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="F75" s="14">
-        <v>212</v>
+        <v>55259</v>
       </c>
       <c r="G75" s="15">
-        <v>2</v>
-      </c>
-      <c r="H75" s="17" t="s">
-        <v>160</v>
+        <v>14964.73</v>
+      </c>
+      <c r="H75" s="16">
+        <v>0.0107660138068</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>13</v>
@@ -3587,6 +3545,27 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F76" s="14">
+        <v>10638</v>
+      </c>
+      <c r="G76" s="15">
+        <v>4186.11</v>
+      </c>
+      <c r="H76" s="16">
+        <v>0.0030115958027</v>
+      </c>
+      <c r="I76" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J76" s="11" t="s">
@@ -3594,28 +3573,28 @@
       </c>
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
-      <c r="B77" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G77" s="9">
-        <v>45104.46</v>
-      </c>
-      <c r="H77" s="10">
-        <v>0.031985645314299996</v>
-      </c>
-      <c r="I77" s="9" t="s">
+      <c r="B77" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="F77" s="14">
+        <v>23400</v>
+      </c>
+      <c r="G77" s="15">
+        <v>4100.57</v>
+      </c>
+      <c r="H77" s="16">
+        <v>0.0029500561143</v>
+      </c>
+      <c r="I77" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J77" s="11" t="s">
@@ -3624,25 +3603,25 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="F78" s="14">
-        <v>253394</v>
+        <v>24152</v>
       </c>
       <c r="G78" s="15">
-        <v>18136.54</v>
+        <v>3602.28</v>
       </c>
       <c r="H78" s="16">
-        <v>0.0128614539598</v>
+        <v>0.0025915734006</v>
       </c>
       <c r="I78" s="15" t="s">
         <v>13</v>
@@ -3653,25 +3632,25 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F79" s="14">
-        <v>43600</v>
+        <v>5209</v>
       </c>
       <c r="G79" s="15">
-        <v>14541.74</v>
+        <v>1848.20</v>
       </c>
       <c r="H79" s="16">
-        <v>0.0103122160845</v>
+        <v>0.0013296428814</v>
       </c>
       <c r="I79" s="15" t="s">
         <v>13</v>
@@ -3682,27 +3661,6 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="C80" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E80" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="F80" s="14">
-        <v>23400</v>
-      </c>
-      <c r="G80" s="15">
-        <v>4818.75</v>
-      </c>
-      <c r="H80" s="16">
-        <v>0.0034171970656</v>
-      </c>
-      <c r="I80" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J80" s="11" t="s">
@@ -3710,28 +3668,28 @@
       </c>
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
-      <c r="B81" s="12" t="s">
+      <c r="B81" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="D81" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="F81" s="14">
-        <v>10638</v>
-      </c>
-      <c r="G81" s="15">
-        <v>3825.57</v>
-      </c>
-      <c r="H81" s="16">
-        <v>0.0027128874871</v>
-      </c>
-      <c r="I81" s="15" t="s">
+      <c r="H81" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="I81" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J81" s="11" t="s">
@@ -3740,27 +3698,6 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="C82" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="D82" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E82" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="F82" s="14">
-        <v>5209</v>
-      </c>
-      <c r="G82" s="15">
-        <v>1974.28</v>
-      </c>
-      <c r="H82" s="16">
-        <v>0.0014000526739</v>
-      </c>
-      <c r="I82" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J82" s="11" t="s">
@@ -3768,28 +3705,28 @@
       </c>
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
-      <c r="B83" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="C83" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="D83" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F83" s="14">
-        <v>8215</v>
-      </c>
-      <c r="G83" s="15">
-        <v>1807.58</v>
-      </c>
-      <c r="H83" s="16">
-        <v>0.0012818380434</v>
-      </c>
-      <c r="I83" s="15" t="s">
+      <c r="B83" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="I83" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J83" s="11" t="s">
@@ -3806,7 +3743,7 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="7" t="s">
-        <v>183</v>
+        <v>14</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>13</v>
@@ -3821,10 +3758,10 @@
         <v>13</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I85" s="9" t="s">
         <v>13</v>
@@ -3843,7 +3780,7 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
       <c r="B87" s="7" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>13</v>
@@ -3858,10 +3795,10 @@
         <v>13</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I87" s="9" t="s">
         <v>13</v>
@@ -3880,7 +3817,7 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
       <c r="B89" s="7" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>13</v>
@@ -3895,10 +3832,10 @@
         <v>13</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I89" s="9" t="s">
         <v>13</v>
@@ -3917,7 +3854,7 @@
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
       <c r="B91" s="7" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>13</v>
@@ -3932,10 +3869,10 @@
         <v>13</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I91" s="9" t="s">
         <v>13</v>
@@ -3954,7 +3891,7 @@
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
       <c r="B93" s="7" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>13</v>
@@ -3969,10 +3906,10 @@
         <v>13</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I93" s="9" t="s">
         <v>13</v>
@@ -3991,7 +3928,7 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
       <c r="B95" s="7" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>13</v>
@@ -4005,11 +3942,11 @@
       <c r="F95" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G95" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>184</v>
+      <c r="G95" s="9">
+        <v>7753.03</v>
+      </c>
+      <c r="H95" s="10">
+        <v>0.0055777303046</v>
       </c>
       <c r="I95" s="9" t="s">
         <v>13</v>
@@ -4028,7 +3965,7 @@
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
       <c r="B97" s="7" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>13</v>
@@ -4043,10 +3980,10 @@
         <v>13</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I97" s="9" t="s">
         <v>13</v>
@@ -4065,7 +4002,7 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
       <c r="B99" s="7" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>13</v>
@@ -4079,11 +4016,11 @@
       <c r="F99" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G99" s="9">
-        <v>12960.77</v>
-      </c>
-      <c r="H99" s="10">
-        <v>0.0091910776055</v>
+      <c r="G99" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>176</v>
       </c>
       <c r="I99" s="9" t="s">
         <v>13</v>
@@ -4102,7 +4039,7 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
       <c r="B101" s="7" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>13</v>
@@ -4116,11 +4053,11 @@
       <c r="F101" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G101" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>184</v>
+      <c r="G101" s="9">
+        <v>7753.03</v>
+      </c>
+      <c r="H101" s="10">
+        <v>0.0055777303046</v>
       </c>
       <c r="I101" s="9" t="s">
         <v>13</v>
@@ -4131,36 +4068,57 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
       <c r="B102" s="12" t="s">
-        <v>13</v>
+        <v>186</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="F102" s="14">
+        <v>2250000</v>
+      </c>
+      <c r="G102" s="15">
+        <v>2234.2</v>
+      </c>
+      <c r="H102" s="16">
+        <v>0.0016073412649</v>
+      </c>
+      <c r="I102" s="15">
+        <v>5.61</v>
       </c>
       <c r="J102" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
-      <c r="B103" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F103" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G103" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I103" s="9" t="s">
-        <v>13</v>
+      <c r="B103" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="D103" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="F103" s="14">
+        <v>2000000</v>
+      </c>
+      <c r="G103" s="15">
+        <v>1992.22</v>
+      </c>
+      <c r="H103" s="16">
+        <v>0.0014332545943</v>
+      </c>
+      <c r="I103" s="15">
+        <v>5.70</v>
       </c>
       <c r="J103" s="11" t="s">
         <v>13</v>
@@ -4168,36 +4126,57 @@
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
       <c r="B104" s="12" t="s">
-        <v>13</v>
+        <v>189</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="F104" s="14">
+        <v>1900000</v>
+      </c>
+      <c r="G104" s="15">
+        <v>1888.41</v>
+      </c>
+      <c r="H104" s="16">
+        <v>0.0013585709954</v>
+      </c>
+      <c r="I104" s="15">
+        <v>5.60</v>
       </c>
       <c r="J104" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
-      <c r="B105" s="7" t="s">
+      <c r="B105" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C105" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="C105" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F105" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G105" s="9">
-        <v>12960.77</v>
-      </c>
-      <c r="H105" s="10">
-        <v>0.0091910776055</v>
-      </c>
-      <c r="I105" s="9" t="s">
-        <v>13</v>
+      <c r="D105" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="F105" s="14">
+        <v>1400000</v>
+      </c>
+      <c r="G105" s="15">
+        <v>1389.96</v>
+      </c>
+      <c r="H105" s="16">
+        <v>0.0009999731736</v>
+      </c>
+      <c r="I105" s="15">
+        <v>5.61</v>
       </c>
       <c r="J105" s="11" t="s">
         <v>13</v>
@@ -4205,28 +4184,28 @@
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
       <c r="B106" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C106" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="C106" s="13" t="s">
-        <v>195</v>
-      </c>
       <c r="D106" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F106" s="14">
-        <v>7500000</v>
+        <v>250000</v>
       </c>
       <c r="G106" s="15">
-        <v>7409.97</v>
+        <v>248.24</v>
       </c>
       <c r="H106" s="16">
-        <v>0.0052547502444</v>
+        <v>0.0001785902764</v>
       </c>
       <c r="I106" s="15">
-        <v>6.52</v>
+        <v>5.61</v>
       </c>
       <c r="J106" s="11" t="s">
         <v>13</v>
@@ -4234,57 +4213,36 @@
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1">
       <c r="B107" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C107" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D107" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="F107" s="14">
-        <v>5000000</v>
-      </c>
-      <c r="G107" s="15">
-        <v>4952.06</v>
-      </c>
-      <c r="H107" s="16">
-        <v>0.0035117333127</v>
-      </c>
-      <c r="I107" s="15">
-        <v>6.43</v>
+        <v>13</v>
       </c>
       <c r="J107" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1">
-      <c r="B108" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="C108" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="D108" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E108" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="F108" s="14">
-        <v>600000</v>
-      </c>
-      <c r="G108" s="15">
-        <v>598.74</v>
-      </c>
-      <c r="H108" s="16">
-        <v>0.0004245940484</v>
-      </c>
-      <c r="I108" s="15">
-        <v>6.42</v>
+      <c r="B108" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H108" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="I108" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J108" s="11" t="s">
         <v>13</v>
@@ -4300,7 +4258,7 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
       <c r="B110" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>13</v>
@@ -4315,10 +4273,10 @@
         <v>13</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="H110" s="10" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I110" s="9" t="s">
         <v>13</v>
@@ -4337,7 +4295,7 @@
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
       <c r="B112" s="7" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>13</v>
@@ -4351,11 +4309,11 @@
       <c r="F112" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G112" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H112" s="10" t="s">
-        <v>184</v>
+      <c r="G112" s="9">
+        <v>20779.24</v>
+      </c>
+      <c r="H112" s="10">
+        <v>0.0149491226862</v>
       </c>
       <c r="I112" s="9" t="s">
         <v>13</v>
@@ -4374,7 +4332,7 @@
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
       <c r="B114" s="7" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>13</v>
@@ -4389,10 +4347,10 @@
         <v>13</v>
       </c>
       <c r="G114" s="9">
-        <v>43251.45</v>
+        <v>2274.82013</v>
       </c>
       <c r="H114" s="10">
-        <v>0.0306715907705</v>
+        <v>0.001636564437</v>
       </c>
       <c r="I114" s="9" t="s">
         <v>13</v>
@@ -4403,6 +4361,20 @@
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
       <c r="B115" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="C115" s="13"/>
+      <c r="D115" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" s="13"/>
+      <c r="G115" s="15">
+        <v>2274.82013</v>
+      </c>
+      <c r="H115" s="16">
+        <v>0.001636564437</v>
+      </c>
+      <c r="I115" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J115" s="11" t="s">
@@ -4410,302 +4382,209 @@
       </c>
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
-      <c r="B116" s="7" t="s">
+      <c r="B116" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J116" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117" spans="2:10" ht="15" customHeight="1">
+      <c r="B117" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="C117" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F117" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" s="19">
+        <v>3197.3684125097934</v>
+      </c>
+      <c r="H117" s="20">
+        <v>0.0023002695320811836</v>
+      </c>
+      <c r="I117" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J117" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118" spans="2:10" ht="15" customHeight="1">
+      <c r="B118" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="C118" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D118" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" s="19">
+        <v>1389997.28854251</v>
+      </c>
+      <c r="H118" s="20">
+        <v>0.999999999995981</v>
+      </c>
+      <c r="I118" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J118" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" spans="2:8" ht="15" customHeight="1">
+      <c r="B120" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="C120" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F120" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H120" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121" spans="2:8" ht="15" customHeight="1">
+      <c r="B121" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C121" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D121" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E121" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F121" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G121" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="H121" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="2:8" ht="15" customHeight="1">
+      <c r="B122" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="C116" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D116" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F116" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G116" s="9">
-        <v>2254.82013</v>
-      </c>
-      <c r="H116" s="10">
-        <v>0.0015989965721</v>
-      </c>
-      <c r="I116" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J116" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="117" spans="2:10" ht="15" customHeight="1">
-      <c r="B117" s="12" t="s">
+      <c r="C122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H122" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123" spans="2:10" ht="15" customHeight="1">
+      <c r="B123" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="C117" s="13"/>
-      <c r="D117" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E117" s="13"/>
-      <c r="G117" s="15">
-        <v>2254.82013</v>
-      </c>
-      <c r="H117" s="16">
-        <v>0.0015989965721</v>
-      </c>
-      <c r="I117" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J117" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="118" spans="2:10" ht="15" customHeight="1">
-      <c r="B118" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J118" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="119" spans="2:10" ht="15" customHeight="1">
-      <c r="B119" s="18" t="s">
+      <c r="C123" s="13"/>
+      <c r="D123" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F123" s="14">
+        <v>1400000</v>
+      </c>
+      <c r="G123" s="15">
+        <v>3358.74</v>
+      </c>
+      <c r="H123" s="16">
+        <v>0.0024163644258</v>
+      </c>
+      <c r="I123" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J123" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="2:10" ht="15" customHeight="1">
+      <c r="B124" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="C119" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D119" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E119" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F119" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G119" s="19">
-        <v>8448.894109189976</v>
-      </c>
-      <c r="H119" s="20">
-        <v>0.005991499072990842</v>
-      </c>
-      <c r="I119" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J119" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="120" spans="2:10" ht="15" customHeight="1">
-      <c r="B120" s="18" t="s">
+      <c r="C124" s="13"/>
+      <c r="D124" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F124" s="14">
+        <v>63750</v>
+      </c>
+      <c r="G124" s="15">
+        <v>914.18</v>
+      </c>
+      <c r="H124" s="16">
+        <v>0.0006576847361</v>
+      </c>
+      <c r="I124" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J124" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128" spans="2:9" ht="15" customHeight="1">
+      <c r="B128" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="C120" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D120" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E120" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F120" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G120" s="19">
-        <v>1410146.94423919</v>
-      </c>
-      <c r="H120" s="20">
-        <v>0.999999999995991</v>
-      </c>
-      <c r="I120" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J120" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="122" spans="2:8" ht="15" customHeight="1">
-      <c r="B122" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="C122" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D122" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E122" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F122" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G122" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H122" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="123" spans="2:8" ht="15" customHeight="1">
-      <c r="B123" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C123" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D123" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="E123" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F123" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G123" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="H123" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="124" spans="2:8" ht="15" customHeight="1">
-      <c r="B124" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="C124" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D124" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E124" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F124" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G124" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H124" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="125" spans="2:10" ht="15" customHeight="1">
-      <c r="B125" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="C125" s="13"/>
-      <c r="D125" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E125" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F125" s="14">
-        <v>550525</v>
-      </c>
-      <c r="G125" s="15">
-        <v>8993.65</v>
-      </c>
-      <c r="H125" s="16">
-        <v>0.0063778105088</v>
-      </c>
-      <c r="I125" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J125" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="126" spans="2:10" ht="15" customHeight="1">
-      <c r="B126" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="C126" s="13"/>
-      <c r="D126" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E126" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F126" s="14">
-        <v>350000</v>
-      </c>
-      <c r="G126" s="15">
-        <v>1882.30</v>
-      </c>
-      <c r="H126" s="16">
-        <v>0.0013348254291</v>
-      </c>
-      <c r="I126" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J126" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="127" spans="2:10" ht="15" customHeight="1">
-      <c r="B127" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="C127" s="13"/>
-      <c r="D127" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F127" s="14">
-        <v>55000</v>
-      </c>
-      <c r="G127" s="15">
-        <v>1585.82</v>
-      </c>
-      <c r="H127" s="16">
-        <v>0.0011245778367</v>
-      </c>
-      <c r="I127" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J127" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="128" spans="2:10" ht="15" customHeight="1">
-      <c r="B128" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="C128" s="13"/>
-      <c r="D128" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E128" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F128" s="14">
-        <v>590000</v>
-      </c>
-      <c r="G128" s="15">
-        <v>991.26</v>
-      </c>
-      <c r="H128" s="16">
-        <v>0.0007029480183</v>
-      </c>
-      <c r="I128" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J128" s="11" t="s">
-        <v>13</v>
-      </c>
+      <c r="C128" s="22"/>
+      <c r="D128" s="22"/>
+      <c r="E128" s="22"/>
+      <c r="F128" s="22"/>
+      <c r="G128" s="22"/>
+      <c r="H128" s="22"/>
+      <c r="I128" s="22"/>
     </row>
     <row r="132" spans="2:9" ht="15" customHeight="1">
       <c r="B132" s="13" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C132" s="22"/>
       <c r="D132" s="22"/>
@@ -4715,9 +4594,31 @@
       <c r="H132" s="22"/>
       <c r="I132" s="22"/>
     </row>
-    <row r="136" spans="2:9" ht="15" customHeight="1">
+    <row r="133" spans="2:8" ht="15" customHeight="1">
+      <c r="B133" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="C133" s="22"/>
+      <c r="D133" s="22"/>
+      <c r="E133" s="22"/>
+      <c r="F133" s="22"/>
+      <c r="G133" s="22"/>
+      <c r="H133" s="22"/>
+    </row>
+    <row r="134" spans="2:8" ht="15" customHeight="1">
+      <c r="B134" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="C134" s="22"/>
+      <c r="D134" s="22"/>
+      <c r="E134" s="22"/>
+      <c r="F134" s="22"/>
+      <c r="G134" s="22"/>
+      <c r="H134" s="22"/>
+    </row>
+    <row r="136" spans="2:8" ht="15" customHeight="1">
       <c r="B136" s="13" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C136" s="22"/>
       <c r="D136" s="22"/>
@@ -4725,45 +4626,47 @@
       <c r="F136" s="22"/>
       <c r="G136" s="22"/>
       <c r="H136" s="22"/>
-      <c r="I136" s="22"/>
-    </row>
-    <row r="137" spans="2:8" ht="15" customHeight="1">
-      <c r="B137" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="C137" s="22"/>
-      <c r="D137" s="22"/>
-      <c r="E137" s="22"/>
-      <c r="F137" s="22"/>
-      <c r="G137" s="22"/>
-      <c r="H137" s="22"/>
-    </row>
-    <row r="138" spans="2:8" ht="15" customHeight="1">
-      <c r="B138" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="C138" s="22"/>
-      <c r="D138" s="22"/>
-      <c r="E138" s="22"/>
-      <c r="F138" s="22"/>
-      <c r="G138" s="22"/>
-      <c r="H138" s="22"/>
-    </row>
-    <row r="140" spans="2:8" ht="15" customHeight="1">
-      <c r="B140" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="C140" s="22"/>
-      <c r="D140" s="22"/>
-      <c r="E140" s="22"/>
-      <c r="F140" s="22"/>
-      <c r="G140" s="22"/>
-      <c r="H140" s="22"/>
+    </row>
+    <row r="138" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B138" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="C138" s="24"/>
+      <c r="D138" s="24"/>
+      <c r="E138" s="24"/>
+      <c r="F138" s="24"/>
+      <c r="G138" s="24"/>
+      <c r="H138" s="24"/>
+    </row>
+    <row r="139" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B139" s="24"/>
+      <c r="C139" s="24"/>
+      <c r="D139" s="24"/>
+      <c r="E139" s="24"/>
+      <c r="F139" s="24"/>
+      <c r="G139" s="24"/>
+      <c r="H139" s="24"/>
+    </row>
+    <row r="140" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B140" s="24"/>
+      <c r="C140" s="24"/>
+      <c r="D140" s="24"/>
+      <c r="E140" s="24"/>
+      <c r="F140" s="24"/>
+      <c r="G140" s="24"/>
+      <c r="H140" s="24"/>
+    </row>
+    <row r="141" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B141" s="24"/>
+      <c r="C141" s="24"/>
+      <c r="D141" s="24"/>
+      <c r="E141" s="24"/>
+      <c r="F141" s="24"/>
+      <c r="G141" s="24"/>
+      <c r="H141" s="24"/>
     </row>
     <row r="142" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B142" s="23" t="s">
-        <v>218</v>
-      </c>
+      <c r="B142" s="24"/>
       <c r="C142" s="24"/>
       <c r="D142" s="24"/>
       <c r="E142" s="24"/>
@@ -4780,116 +4683,80 @@
       <c r="G143" s="24"/>
       <c r="H143" s="24"/>
     </row>
-    <row r="144" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B144" s="24"/>
-      <c r="C144" s="24"/>
-      <c r="D144" s="24"/>
-      <c r="E144" s="24"/>
-      <c r="F144" s="24"/>
-      <c r="G144" s="24"/>
-      <c r="H144" s="24"/>
-    </row>
-    <row r="145" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B145" s="24"/>
-      <c r="C145" s="24"/>
-      <c r="D145" s="24"/>
-      <c r="E145" s="24"/>
-      <c r="F145" s="24"/>
-      <c r="G145" s="24"/>
-      <c r="H145" s="24"/>
-    </row>
-    <row r="146" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B146" s="24"/>
-      <c r="C146" s="24"/>
-      <c r="D146" s="24"/>
-      <c r="E146" s="24"/>
-      <c r="F146" s="24"/>
-      <c r="G146" s="24"/>
-      <c r="H146" s="24"/>
-    </row>
-    <row r="147" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B147" s="24"/>
-      <c r="C147" s="24"/>
-      <c r="D147" s="24"/>
-      <c r="E147" s="24"/>
-      <c r="F147" s="24"/>
-      <c r="G147" s="24"/>
-      <c r="H147" s="24"/>
-    </row>
-    <row r="149" spans="2:8" ht="15" customHeight="1">
-      <c r="B149" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="C149" s="22"/>
-      <c r="D149" s="22"/>
-      <c r="E149" s="22"/>
-      <c r="F149" s="22"/>
-      <c r="G149" s="22"/>
-      <c r="H149" s="22"/>
-    </row>
-    <row r="150" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B150" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="C150" s="22"/>
-      <c r="D150" s="22"/>
-      <c r="E150" s="22"/>
-      <c r="F150" s="22"/>
-      <c r="G150" s="22"/>
-      <c r="H150" s="22"/>
-    </row>
-    <row r="151" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B151" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="C151" s="22"/>
-      <c r="D151" s="22"/>
-      <c r="E151" s="22"/>
-      <c r="F151" s="22"/>
-      <c r="G151" s="22"/>
-      <c r="H151" s="22"/>
-    </row>
-    <row r="152" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B152" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="C152" s="22"/>
-      <c r="D152" s="22"/>
-      <c r="E152" s="22"/>
-      <c r="F152" s="22"/>
-      <c r="G152" s="22"/>
-      <c r="H152" s="22"/>
-    </row>
-    <row r="155" ht="15">
-      <c r="B155" s="22" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="170" ht="15">
-      <c r="B170" s="22" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="171" ht="15">
-      <c r="B171" s="22" t="s">
-        <v>225</v>
+    <row r="145" spans="2:8" ht="15" customHeight="1">
+      <c r="B145" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C145" s="22"/>
+      <c r="D145" s="22"/>
+      <c r="E145" s="22"/>
+      <c r="F145" s="22"/>
+      <c r="G145" s="22"/>
+      <c r="H145" s="22"/>
+    </row>
+    <row r="146" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B146" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="C146" s="22"/>
+      <c r="D146" s="22"/>
+      <c r="E146" s="22"/>
+      <c r="F146" s="22"/>
+      <c r="G146" s="22"/>
+      <c r="H146" s="22"/>
+    </row>
+    <row r="147" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B147" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="C147" s="22"/>
+      <c r="D147" s="22"/>
+      <c r="E147" s="22"/>
+      <c r="F147" s="22"/>
+      <c r="G147" s="22"/>
+      <c r="H147" s="22"/>
+    </row>
+    <row r="148" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B148" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="C148" s="22"/>
+      <c r="D148" s="22"/>
+      <c r="E148" s="22"/>
+      <c r="F148" s="22"/>
+      <c r="G148" s="22"/>
+      <c r="H148" s="22"/>
+    </row>
+    <row r="151" ht="15">
+      <c r="B151" s="22" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="166" ht="15">
+      <c r="B166" s="22" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="167" ht="15">
+      <c r="B167" s="22" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B150:H150"/>
-    <mergeCell ref="B151:H151"/>
-    <mergeCell ref="B152:H152"/>
-    <mergeCell ref="B137:H137"/>
-    <mergeCell ref="B138:H138"/>
-    <mergeCell ref="B140:H140"/>
-    <mergeCell ref="B142:H147"/>
-    <mergeCell ref="B149:H149"/>
+    <mergeCell ref="B146:H146"/>
+    <mergeCell ref="B147:H147"/>
+    <mergeCell ref="B148:H148"/>
+    <mergeCell ref="B133:H133"/>
+    <mergeCell ref="B134:H134"/>
+    <mergeCell ref="B136:H136"/>
+    <mergeCell ref="B138:H143"/>
+    <mergeCell ref="B145:H145"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B128:I128"/>
     <mergeCell ref="B132:I132"/>
-    <mergeCell ref="B136:I136"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
